--- a/Excel/PhantomConfig.xlsx
+++ b/Excel/PhantomConfig.xlsx
@@ -1,54 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>admin</author>
-  </authors>
-  <commentList>
-    <comment ref="E3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
--1 没有
-0 随机
-&gt;0 对应模型</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
   <si>
     <t>ID</t>
   </si>
@@ -56,6 +35,12 @@
     <t>Name</t>
   </si>
   <si>
+    <t>RequireCycle</t>
+  </si>
+  <si>
+    <t>Desc</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -77,23 +62,86 @@
     <t>幻神战士</t>
   </si>
   <si>
+    <t>只有战士技能，才能造成伤害</t>
+  </si>
+  <si>
     <t>幻神法师</t>
   </si>
   <si>
+    <t>只有法师技能，才能造成伤害</t>
+  </si>
+  <si>
     <t>幻神道士</t>
+  </si>
+  <si>
+    <t>只有道士技能，才能造成伤害</t>
+  </si>
+  <si>
+    <t>幻神猫王</t>
+  </si>
+  <si>
+    <t>幻神花王</t>
+  </si>
+  <si>
+    <t>幻神雪王</t>
+  </si>
+  <si>
+    <t>幻神蝠王</t>
+  </si>
+  <si>
+    <t>幻神骷髅王</t>
+  </si>
+  <si>
+    <t>幻神尸王</t>
+  </si>
+  <si>
+    <t>幻神蛇王</t>
+  </si>
+  <si>
+    <t>幻神狼王</t>
+  </si>
+  <si>
+    <t>幻神虫王</t>
+  </si>
+  <si>
+    <t>幻神鹰王</t>
+  </si>
+  <si>
+    <t>幻神角虫王</t>
+  </si>
+  <si>
+    <t>幻神蜈蚣王</t>
+  </si>
+  <si>
+    <t>幻神钳虫王</t>
+  </si>
+  <si>
+    <t>幻神蠕虫王</t>
+  </si>
+  <si>
+    <t>幻神猪王</t>
+  </si>
+  <si>
+    <t>幻神猪皇</t>
+  </si>
+  <si>
+    <t>幻神蝎王</t>
+  </si>
+  <si>
+    <t>幻神恶魔教主</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,6 +154,13 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -115,6 +170,19 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -257,17 +325,6 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -594,144 +651,150 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1052,274 +1115,459 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9" style="2"/>
+    <col min="1" max="1" width="6.875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9" style="3"/>
     <col min="3" max="3" width="9.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="30.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9.625" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2"/>
+    <col min="5" max="5" width="12.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="39.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.625" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:7">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:7">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:7">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:7">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="E1" s="2"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:7">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="E2" s="2"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:7">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" s="1" customFormat="1" spans="1:7">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
+      <c r="E3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:7">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:7">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3" t="s">
+      <c r="E4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:7">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:7">
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:7">
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:7">
+      <c r="C8" s="2">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" customHeight="1" spans="1:7">
+      <c r="C9" s="2">
         <v>4</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" customFormat="1" ht="27" customHeight="1" spans="3:5">
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="D9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:7">
+      <c r="C10" s="2">
         <v>5</v>
       </c>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="3:4">
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="D10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:7">
+      <c r="C11" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="3:4">
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="D11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:7">
+      <c r="C12" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="3:5">
-      <c r="C9">
-        <v>4</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="D12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" customHeight="1" spans="1:7">
+      <c r="C13" s="2">
         <v>8</v>
       </c>
-      <c r="E9"/>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="3:5">
-      <c r="C10">
-        <v>5</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="D13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:7">
+      <c r="C14" s="2">
         <v>9</v>
       </c>
-      <c r="E10"/>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="3:5">
-      <c r="C11">
-        <v>6</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="D14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" customHeight="1" spans="1:7">
+      <c r="C15" s="2">
         <v>10</v>
       </c>
-      <c r="E11"/>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="3:5">
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="3:5">
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13"/>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="3:5">
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14"/>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="3:5">
-      <c r="C15"/>
-      <c r="D15"/>
-      <c r="E15"/>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="3:5">
-      <c r="C16"/>
-      <c r="D16"/>
-      <c r="E16"/>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="3:5">
-      <c r="C17"/>
-      <c r="D17"/>
-      <c r="E17"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="3:5">
-      <c r="C18"/>
-      <c r="D18"/>
-      <c r="E18"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="3:5">
-      <c r="C19"/>
-      <c r="D19"/>
-      <c r="E19"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="3:5">
-      <c r="C20"/>
-      <c r="D20"/>
-      <c r="E20"/>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="3:5">
-      <c r="C21"/>
-      <c r="D21"/>
-      <c r="E21"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="3:5">
-      <c r="C22"/>
-      <c r="D22"/>
-      <c r="E22"/>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="3:5">
-      <c r="C23"/>
-      <c r="D23"/>
-      <c r="E23"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="3:5">
-      <c r="C24"/>
-      <c r="D24"/>
-      <c r="E24"/>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="3:5">
-      <c r="C25"/>
-      <c r="D25"/>
-      <c r="E25"/>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="3:5">
-      <c r="C26"/>
-      <c r="D26"/>
-      <c r="E26"/>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="3:5">
-      <c r="C27"/>
-      <c r="D27"/>
-      <c r="E27"/>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="3:5">
-      <c r="C28"/>
-      <c r="D28"/>
-      <c r="E28"/>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="3:5">
-      <c r="C29"/>
-      <c r="D29"/>
-      <c r="E29"/>
-    </row>
-    <row r="30" ht="24" customHeight="1" spans="3:5">
-      <c r="C30"/>
-      <c r="D30"/>
-      <c r="E30"/>
-    </row>
-    <row r="31" ht="24" customHeight="1" spans="3:5">
-      <c r="C31"/>
-      <c r="D31"/>
-      <c r="E31"/>
-    </row>
-    <row r="32" ht="24" customHeight="1" spans="3:5">
-      <c r="C32"/>
-      <c r="D32"/>
-      <c r="E32"/>
-    </row>
-    <row r="33" ht="24" customHeight="1" spans="3:5">
-      <c r="C33"/>
-      <c r="D33"/>
-      <c r="E33"/>
-    </row>
-    <row r="34" ht="24" customHeight="1" spans="3:5">
-      <c r="C34"/>
-      <c r="D34"/>
-      <c r="E34"/>
-    </row>
-    <row r="35" ht="24" customHeight="1" spans="3:5">
-      <c r="C35"/>
-      <c r="D35"/>
-      <c r="E35"/>
-    </row>
-    <row r="36" ht="24" customHeight="1" spans="3:5">
-      <c r="C36"/>
-      <c r="D36"/>
-      <c r="E36"/>
-    </row>
-    <row r="37" ht="24" customHeight="1" spans="3:5">
-      <c r="C37"/>
-      <c r="D37"/>
-      <c r="E37"/>
-    </row>
-    <row r="38" ht="24" customHeight="1" spans="3:5">
-      <c r="C38"/>
-      <c r="D38"/>
-      <c r="E38"/>
-    </row>
-    <row r="39" ht="24" customHeight="1" spans="3:5">
-      <c r="C39"/>
-      <c r="D39"/>
-      <c r="E39"/>
-    </row>
-    <row r="40" ht="24" customHeight="1" spans="3:5">
-      <c r="C40"/>
-      <c r="D40"/>
-      <c r="E40"/>
+      <c r="D15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" customHeight="1" spans="1:7">
+      <c r="C16" s="2">
+        <v>11</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="2">
+        <v>0</v>
+      </c>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" customHeight="1" spans="3:6">
+      <c r="C17" s="2">
+        <v>12</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" customHeight="1" spans="3:6">
+      <c r="C18" s="2">
+        <v>13</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" customHeight="1" spans="3:6">
+      <c r="C19" s="2">
+        <v>14</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2"/>
+    </row>
+    <row r="20" customHeight="1" spans="3:6">
+      <c r="C20" s="2">
+        <v>15</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="2">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" customHeight="1" spans="3:6">
+      <c r="C21" s="2">
+        <v>16</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="2">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" customHeight="1" spans="3:6">
+      <c r="C22" s="2">
+        <v>17</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="2">
+        <v>12</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:6">
+      <c r="C23" s="2">
+        <v>18</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="2">
+        <v>12</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:6">
+      <c r="C24" s="2">
+        <v>19</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="2">
+        <v>12</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:6">
+      <c r="C25" s="2">
+        <v>20</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="2">
+        <v>12</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:6">
+      <c r="C26" s="2">
+        <v>21</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="2">
+        <v>12</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:6">
+      <c r="C27" s="2">
+        <v>22</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="2">
+        <v>12</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:6">
+      <c r="C28" s="2">
+        <v>23</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="2">
+        <v>15</v>
+      </c>
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" customHeight="1" spans="3:6">
+      <c r="C29" s="2">
+        <v>24</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="2">
+        <v>15</v>
+      </c>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" customHeight="1" spans="3:6">
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" customHeight="1" spans="3:6">
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" customHeight="1" spans="3:6">
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" customHeight="1" spans="3:6">
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" customHeight="1" spans="3:6">
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" customHeight="1" spans="3:6">
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+    </row>
+    <row r="36" customHeight="1" spans="3:6">
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+    </row>
+    <row r="37" customHeight="1" spans="3:6">
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" customHeight="1" spans="3:6">
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+    </row>
+    <row r="39" customHeight="1" spans="3:6">
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+    </row>
+    <row r="40" customHeight="1" spans="3:6">
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 C3:C5 D4:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 F3:F5 C3:D5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Excel/PhantomConfig.xlsx
+++ b/Excel/PhantomConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>ID</t>
   </si>
@@ -75,60 +75,6 @@
   </si>
   <si>
     <t>只有道士技能，才能造成伤害</t>
-  </si>
-  <si>
-    <t>幻神猫王</t>
-  </si>
-  <si>
-    <t>幻神花王</t>
-  </si>
-  <si>
-    <t>幻神雪王</t>
-  </si>
-  <si>
-    <t>幻神蝠王</t>
-  </si>
-  <si>
-    <t>幻神骷髅王</t>
-  </si>
-  <si>
-    <t>幻神尸王</t>
-  </si>
-  <si>
-    <t>幻神蛇王</t>
-  </si>
-  <si>
-    <t>幻神狼王</t>
-  </si>
-  <si>
-    <t>幻神虫王</t>
-  </si>
-  <si>
-    <t>幻神鹰王</t>
-  </si>
-  <si>
-    <t>幻神角虫王</t>
-  </si>
-  <si>
-    <t>幻神蜈蚣王</t>
-  </si>
-  <si>
-    <t>幻神钳虫王</t>
-  </si>
-  <si>
-    <t>幻神蠕虫王</t>
-  </si>
-  <si>
-    <t>幻神猪王</t>
-  </si>
-  <si>
-    <t>幻神猪皇</t>
-  </si>
-  <si>
-    <t>幻神蝎王</t>
-  </si>
-  <si>
-    <t>幻神恶魔教主</t>
   </si>
 </sst>
 </file>
@@ -781,7 +727,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -794,7 +740,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1268,302 +1213,171 @@
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:7">
-      <c r="C12" s="2">
-        <v>7</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="2">
-        <v>0</v>
-      </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
       <c r="F12" s="2"/>
     </row>
     <row r="13" customHeight="1" spans="1:7">
-      <c r="C13" s="2">
-        <v>8</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="2">
-        <v>0</v>
-      </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
     <row r="14" customHeight="1" spans="1:7">
-      <c r="C14" s="2">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
       <c r="F14" s="2"/>
     </row>
     <row r="15" customHeight="1" spans="1:7">
-      <c r="C15" s="2">
-        <v>10</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="2">
-        <v>0</v>
-      </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
       <c r="F15" s="2"/>
     </row>
     <row r="16" customHeight="1" spans="1:7">
-      <c r="C16" s="2">
-        <v>11</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
     <row r="17" customHeight="1" spans="3:6">
-      <c r="C17" s="2">
-        <v>12</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="2">
-        <v>0</v>
-      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
     <row r="18" customHeight="1" spans="3:6">
-      <c r="C18" s="2">
-        <v>13</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0</v>
-      </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
       <c r="F18" s="2"/>
     </row>
     <row r="19" customHeight="1" spans="3:6">
-      <c r="C19" s="2">
-        <v>14</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="2">
-        <v>0</v>
-      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
     <row r="20" customHeight="1" spans="3:6">
-      <c r="C20" s="2">
-        <v>15</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="2">
-        <v>0</v>
-      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
     <row r="21" customHeight="1" spans="3:6">
-      <c r="C21" s="2">
-        <v>16</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="2">
-        <v>0</v>
-      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
     <row r="22" customHeight="1" spans="3:6">
-      <c r="C22" s="2">
-        <v>17</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="2">
-        <v>12</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
     </row>
     <row r="23" customHeight="1" spans="3:6">
-      <c r="C23" s="2">
-        <v>18</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="2">
-        <v>12</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
     </row>
     <row r="24" customHeight="1" spans="3:6">
-      <c r="C24" s="2">
-        <v>19</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E24" s="2">
-        <v>12</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
     </row>
     <row r="25" customHeight="1" spans="3:6">
-      <c r="C25" s="2">
-        <v>20</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" s="2">
-        <v>12</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
     </row>
     <row r="26" customHeight="1" spans="3:6">
-      <c r="C26" s="2">
-        <v>21</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" s="2">
-        <v>12</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
     </row>
     <row r="27" customHeight="1" spans="3:6">
-      <c r="C27" s="2">
-        <v>22</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27" s="2">
-        <v>12</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
     </row>
     <row r="28" customHeight="1" spans="3:6">
-      <c r="C28" s="2">
-        <v>23</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E28" s="2">
-        <v>15</v>
-      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
     <row r="29" customHeight="1" spans="3:6">
-      <c r="C29" s="2">
-        <v>24</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E29" s="2">
-        <v>15</v>
-      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
     <row r="30" customHeight="1" spans="3:6">
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
     <row r="31" customHeight="1" spans="3:6">
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
       <c r="F31" s="2"/>
     </row>
     <row r="32" customHeight="1" spans="3:6">
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
       <c r="F32" s="2"/>
     </row>
     <row r="33" customHeight="1" spans="3:6">
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
       <c r="F33" s="2"/>
     </row>
     <row r="34" customHeight="1" spans="3:6">
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
       <c r="F34" s="2"/>
     </row>
     <row r="35" customHeight="1" spans="3:6">
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
       <c r="F35" s="2"/>
     </row>
     <row r="36" customHeight="1" spans="3:6">
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
       <c r="F36" s="2"/>
     </row>
     <row r="37" customHeight="1" spans="3:6">
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
       <c r="F37" s="2"/>
     </row>
     <row r="38" customHeight="1" spans="3:6">
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
       <c r="F38" s="2"/>
     </row>
     <row r="39" customHeight="1" spans="3:6">
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
       <c r="F39" s="2"/>
     </row>
     <row r="40" customHeight="1" spans="3:6">
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
       <c r="F40" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3 E4 E5 F3:F5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
